--- a/public/exports-from-60/29188599.xlsx
+++ b/public/exports-from-60/29188599.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -24589,12 +24589,12 @@
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592261</t>
+          <t xml:space="preserve">311592264</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M328" t="inlineStr">
@@ -24664,12 +24664,12 @@
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592262</t>
+          <t xml:space="preserve">311592264</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M329" t="inlineStr">
@@ -24739,12 +24739,12 @@
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592262</t>
+          <t xml:space="preserve">311592264</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M330" t="inlineStr">
@@ -24814,12 +24814,12 @@
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592263</t>
+          <t xml:space="preserve">311592264</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M331" t="inlineStr">
@@ -24889,12 +24889,12 @@
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592263</t>
+          <t xml:space="preserve">311592264</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M332" t="inlineStr">
@@ -27139,7 +27139,7 @@
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
@@ -27214,7 +27214,7 @@
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
@@ -27289,7 +27289,7 @@
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
@@ -27364,7 +27364,7 @@
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
@@ -27439,7 +27439,7 @@
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
@@ -27514,7 +27514,7 @@
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
@@ -27589,7 +27589,7 @@
       </c>
       <c r="K368" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
@@ -27739,7 +27739,7 @@
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
@@ -27814,7 +27814,7 @@
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
@@ -27889,7 +27889,7 @@
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
@@ -27964,7 +27964,7 @@
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
@@ -28039,7 +28039,7 @@
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
@@ -28114,7 +28114,7 @@
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
@@ -28189,7 +28189,7 @@
       </c>
       <c r="K376" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
@@ -28264,7 +28264,7 @@
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
@@ -28339,12 +28339,12 @@
       </c>
       <c r="K378" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615356</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M378" t="inlineStr">
@@ -28414,12 +28414,12 @@
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615354</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M379" t="inlineStr">
@@ -28489,7 +28489,7 @@
       </c>
       <c r="K380" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
@@ -28564,7 +28564,7 @@
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
@@ -28639,7 +28639,7 @@
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
@@ -28789,7 +28789,7 @@
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
@@ -28864,7 +28864,7 @@
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
@@ -28939,7 +28939,7 @@
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
@@ -29014,7 +29014,7 @@
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
@@ -29089,7 +29089,7 @@
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
@@ -29164,7 +29164,7 @@
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
@@ -29239,7 +29239,7 @@
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
@@ -29314,7 +29314,7 @@
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="K392" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
@@ -29464,7 +29464,7 @@
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">

--- a/public/exports-from-60/29188599.xlsx
+++ b/public/exports-from-60/29188599.xlsx
@@ -24589,12 +24589,12 @@
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592264</t>
+          <t xml:space="preserve">311592261</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
@@ -24664,12 +24664,12 @@
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592264</t>
+          <t xml:space="preserve">311592262</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
@@ -24739,12 +24739,12 @@
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592264</t>
+          <t xml:space="preserve">311592262</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
@@ -24814,12 +24814,12 @@
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592264</t>
+          <t xml:space="preserve">311592263</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
@@ -24889,12 +24889,12 @@
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592264</t>
+          <t xml:space="preserve">311592263</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
@@ -28414,12 +28414,12 @@
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615354</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M379" t="inlineStr">
@@ -28489,12 +28489,12 @@
       </c>
       <c r="K380" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615359</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M380" t="inlineStr">

--- a/public/exports-from-60/29188599.xlsx
+++ b/public/exports-from-60/29188599.xlsx
@@ -27139,7 +27139,7 @@
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
@@ -27214,7 +27214,7 @@
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
@@ -27289,7 +27289,7 @@
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
@@ -27364,7 +27364,7 @@
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
@@ -27439,7 +27439,7 @@
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
@@ -27514,7 +27514,7 @@
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
@@ -27589,7 +27589,7 @@
       </c>
       <c r="K368" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
@@ -27739,7 +27739,7 @@
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
@@ -27814,7 +27814,7 @@
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
@@ -27889,7 +27889,7 @@
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
@@ -27964,7 +27964,7 @@
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
@@ -28039,7 +28039,7 @@
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
@@ -28114,7 +28114,7 @@
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
@@ -28189,7 +28189,7 @@
       </c>
       <c r="K376" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
@@ -28264,7 +28264,7 @@
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
@@ -28339,12 +28339,12 @@
       </c>
       <c r="K378" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615356</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M378" t="inlineStr">
@@ -28489,12 +28489,12 @@
       </c>
       <c r="K380" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615359</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M380" t="inlineStr">
@@ -28564,7 +28564,7 @@
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
@@ -28639,7 +28639,7 @@
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
@@ -28789,7 +28789,7 @@
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
@@ -28864,7 +28864,7 @@
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
@@ -28939,7 +28939,7 @@
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
@@ -29014,7 +29014,7 @@
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
@@ -29089,7 +29089,7 @@
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
@@ -29164,7 +29164,7 @@
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
@@ -29239,7 +29239,7 @@
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
@@ -29314,7 +29314,7 @@
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="K392" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
@@ -29464,7 +29464,7 @@
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
